--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichaelBurke\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45251797-E1CD-41E2-9437-D4EE6E4CA973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F57A54A-3313-4E07-AEC7-E0A9CF12BED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -442,527 +442,527 @@
       <c r="A2" s="4">
         <v>46023</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>60.26</v>
       </c>
-      <c r="C2" s="2">
-        <v>4.6870000000000003</v>
+      <c r="C2">
+        <v>7.7126000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46054</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>64.522999999999996</v>
       </c>
-      <c r="C3" s="2">
-        <v>7.46</v>
+      <c r="C3">
+        <v>3.8382000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46082</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>90.997</v>
       </c>
-      <c r="C4" s="2">
-        <v>2.9689999999999999</v>
+      <c r="C4">
+        <v>3.0581999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46113</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>98.06</v>
       </c>
-      <c r="C5" s="2">
-        <v>3.0950000000000002</v>
+      <c r="C5">
+        <v>2.7736999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46143</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>98.513999999999996</v>
       </c>
-      <c r="C6" s="2">
-        <v>2.5590000000000002</v>
+      <c r="C6">
+        <v>2.8881999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>46174</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>81.790000000000006</v>
       </c>
-      <c r="C7" s="2">
-        <v>3.04</v>
+      <c r="C7">
+        <v>3.1429999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46204</v>
       </c>
-      <c r="B8" s="2">
-        <v>79.25</v>
-      </c>
-      <c r="C8" s="2">
-        <v>3.2309999999999999</v>
+      <c r="B8">
+        <v>78.540999999999997</v>
+      </c>
+      <c r="C8">
+        <v>3.0176666600000002</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46235</v>
       </c>
-      <c r="B9" s="2">
-        <v>83.653000000000006</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2.7250000000000001</v>
+      <c r="B9">
+        <v>78.563000000000002</v>
+      </c>
+      <c r="C9">
+        <v>2.7669999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46266</v>
       </c>
-      <c r="B10" s="2">
-        <v>81.366</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2.722</v>
+      <c r="B10">
+        <v>76.644000000000005</v>
+      </c>
+      <c r="C10">
+        <v>2.7879999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46296</v>
       </c>
-      <c r="B11" s="2">
-        <v>78.974999999999994</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2.7690000000000001</v>
+      <c r="B11">
+        <v>74.792000000000002</v>
+      </c>
+      <c r="C11">
+        <v>2.823</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46327</v>
       </c>
-      <c r="B12" s="2">
-        <v>77.375</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3.0190000000000001</v>
+      <c r="B12">
+        <v>73.572999999999993</v>
+      </c>
+      <c r="C12">
+        <v>3.0369999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46357</v>
       </c>
-      <c r="B13" s="2">
-        <v>75.914000000000001</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3.7320000000000002</v>
+      <c r="B13">
+        <v>72.459999999999994</v>
+      </c>
+      <c r="C13">
+        <v>3.7519999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46388</v>
       </c>
-      <c r="B14" s="2">
-        <v>74.795000000000002</v>
-      </c>
-      <c r="C14" s="2">
-        <v>4.21</v>
+      <c r="B14">
+        <v>71.602000000000004</v>
+      </c>
+      <c r="C14">
+        <v>4.2080000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46419</v>
       </c>
-      <c r="B15" s="2">
-        <v>74.058000000000007</v>
-      </c>
-      <c r="C15" s="2">
-        <v>3.8319999999999999</v>
+      <c r="B15">
+        <v>71.036000000000001</v>
+      </c>
+      <c r="C15">
+        <v>3.8250000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46447</v>
       </c>
-      <c r="B16" s="2">
-        <v>73.275000000000006</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3.0110000000000001</v>
+      <c r="B16">
+        <v>70.438999999999993</v>
+      </c>
+      <c r="C16">
+        <v>3.0030000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>46478</v>
       </c>
-      <c r="B17" s="2">
-        <v>72.602999999999994</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2.863</v>
+      <c r="B17">
+        <v>69.933999999999997</v>
+      </c>
+      <c r="C17">
+        <v>2.85</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46508</v>
       </c>
-      <c r="B18" s="2">
-        <v>72.087000000000003</v>
-      </c>
-      <c r="C18" s="2">
-        <v>2.8610000000000002</v>
+      <c r="B18">
+        <v>69.546000000000006</v>
+      </c>
+      <c r="C18">
+        <v>2.847</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>46539</v>
       </c>
-      <c r="B19" s="2">
-        <v>71.600999999999999</v>
-      </c>
-      <c r="C19" s="2">
-        <v>2.9950000000000001</v>
+      <c r="B19">
+        <v>69.186000000000007</v>
+      </c>
+      <c r="C19">
+        <v>2.9809999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>46569</v>
       </c>
-      <c r="B20" s="2">
-        <v>71.123999999999995</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3.2010000000000001</v>
+      <c r="B20">
+        <v>68.84</v>
+      </c>
+      <c r="C20">
+        <v>3.1869999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>46600</v>
       </c>
-      <c r="B21" s="2">
-        <v>70.748999999999995</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3.2650000000000001</v>
+      <c r="B21">
+        <v>68.576999999999998</v>
+      </c>
+      <c r="C21">
+        <v>3.254</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>46631</v>
       </c>
-      <c r="B22" s="2">
-        <v>70.387</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3.2410000000000001</v>
+      <c r="B22">
+        <v>68.326999999999998</v>
+      </c>
+      <c r="C22">
+        <v>3.23</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>46661</v>
       </c>
-      <c r="B23" s="2">
-        <v>70.087000000000003</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3.3170000000000002</v>
+      <c r="B23">
+        <v>68.113</v>
+      </c>
+      <c r="C23">
+        <v>3.306</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>46692</v>
       </c>
-      <c r="B24" s="2">
-        <v>69.816999999999993</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3.5579999999999998</v>
+      <c r="B24">
+        <v>67.92</v>
+      </c>
+      <c r="C24">
+        <v>3.55</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>46722</v>
       </c>
-      <c r="B25" s="2">
-        <v>69.507999999999996</v>
-      </c>
-      <c r="C25" s="2">
-        <v>4.22</v>
+      <c r="B25">
+        <v>67.697000000000003</v>
+      </c>
+      <c r="C25">
+        <v>4.2060000000000004</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>46753</v>
       </c>
-      <c r="B26" s="2">
-        <v>69.239000000000004</v>
-      </c>
-      <c r="C26" s="2">
-        <v>4.6669999999999998</v>
+      <c r="B26">
+        <v>67.507000000000005</v>
+      </c>
+      <c r="C26">
+        <v>4.6459999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>46784</v>
       </c>
-      <c r="B27" s="2">
-        <v>69.010000000000005</v>
-      </c>
-      <c r="C27" s="2">
-        <v>4.2270000000000003</v>
+      <c r="B27">
+        <v>67.349999999999994</v>
+      </c>
+      <c r="C27">
+        <v>4.2009999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>46813</v>
       </c>
-      <c r="B28" s="2">
-        <v>68.760000000000005</v>
-      </c>
-      <c r="C28" s="2">
-        <v>3.4319999999999999</v>
+      <c r="B28">
+        <v>67.180999999999997</v>
+      </c>
+      <c r="C28">
+        <v>3.4159999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>46844</v>
       </c>
-      <c r="B29" s="2">
-        <v>68.566999999999993</v>
-      </c>
-      <c r="C29" s="2">
-        <v>3.161</v>
+      <c r="B29">
+        <v>67.046000000000006</v>
+      </c>
+      <c r="C29">
+        <v>3.1480000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>46874</v>
       </c>
-      <c r="B30" s="2">
-        <v>68.37</v>
-      </c>
-      <c r="C30" s="2">
-        <v>3.1379999999999999</v>
+      <c r="B30">
+        <v>66.906000000000006</v>
+      </c>
+      <c r="C30">
+        <v>3.1259999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>46905</v>
       </c>
-      <c r="B31" s="2">
-        <v>68.134</v>
-      </c>
-      <c r="C31" s="2">
-        <v>3.2679999999999998</v>
+      <c r="B31">
+        <v>66.733000000000004</v>
+      </c>
+      <c r="C31">
+        <v>3.2570000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>46935</v>
       </c>
-      <c r="B32" s="2">
-        <v>67.947000000000003</v>
-      </c>
-      <c r="C32" s="2">
-        <v>3.4780000000000002</v>
+      <c r="B32">
+        <v>66.597999999999999</v>
+      </c>
+      <c r="C32">
+        <v>3.47</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>46966</v>
       </c>
-      <c r="B33" s="2">
-        <v>67.778000000000006</v>
-      </c>
-      <c r="C33" s="2">
-        <v>3.55</v>
+      <c r="B33">
+        <v>66.486999999999995</v>
+      </c>
+      <c r="C33">
+        <v>3.5419999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>46997</v>
       </c>
-      <c r="B34" s="2">
-        <v>67.614999999999995</v>
-      </c>
-      <c r="C34" s="2">
-        <v>3.5270000000000001</v>
+      <c r="B34">
+        <v>66.379000000000005</v>
+      </c>
+      <c r="C34">
+        <v>3.5190000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>47027</v>
       </c>
-      <c r="B35" s="2">
-        <v>67.484999999999999</v>
-      </c>
-      <c r="C35" s="2">
-        <v>3.5859999999999999</v>
+      <c r="B35">
+        <v>66.290999999999997</v>
+      </c>
+      <c r="C35">
+        <v>3.5760000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>47058</v>
       </c>
-      <c r="B36" s="2">
-        <v>67.33</v>
-      </c>
-      <c r="C36" s="2">
-        <v>3.7839999999999998</v>
+      <c r="B36">
+        <v>66.186999999999998</v>
+      </c>
+      <c r="C36">
+        <v>3.782</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>47088</v>
       </c>
-      <c r="B37" s="2">
-        <v>67.153999999999996</v>
-      </c>
-      <c r="C37" s="2">
-        <v>4.3899999999999997</v>
+      <c r="B37">
+        <v>66.055000000000007</v>
+      </c>
+      <c r="C37">
+        <v>4.3860000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>47119</v>
       </c>
-      <c r="B38" s="2">
-        <v>67.003</v>
-      </c>
-      <c r="C38" s="2">
-        <v>4.8079999999999998</v>
+      <c r="B38">
+        <v>65.936999999999998</v>
+      </c>
+      <c r="C38">
+        <v>4.8010000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>47150</v>
       </c>
-      <c r="B39" s="2">
-        <v>66.866</v>
-      </c>
-      <c r="C39" s="2">
-        <v>4.3810000000000002</v>
+      <c r="B39">
+        <v>65.837999999999994</v>
+      </c>
+      <c r="C39">
+        <v>4.3760000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>47178</v>
       </c>
-      <c r="B40" s="2">
-        <v>66.72</v>
-      </c>
-      <c r="C40" s="2">
-        <v>3.4809999999999999</v>
+      <c r="B40">
+        <v>65.739999999999995</v>
+      </c>
+      <c r="C40">
+        <v>3.4849999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>47209</v>
       </c>
-      <c r="B41" s="2">
-        <v>66.576999999999998</v>
-      </c>
-      <c r="C41" s="2">
-        <v>3.1829999999999998</v>
+      <c r="B41">
+        <v>65.649000000000001</v>
+      </c>
+      <c r="C41">
+        <v>3.1840000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>47239</v>
       </c>
-      <c r="B42" s="2">
-        <v>66.424000000000007</v>
-      </c>
-      <c r="C42" s="2">
-        <v>3.161</v>
+      <c r="B42">
+        <v>65.528999999999996</v>
+      </c>
+      <c r="C42">
+        <v>3.1619999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>47270</v>
       </c>
-      <c r="B43" s="2">
-        <v>66.254999999999995</v>
-      </c>
-      <c r="C43" s="2">
-        <v>3.2709999999999999</v>
+      <c r="B43">
+        <v>65.367999999999995</v>
+      </c>
+      <c r="C43">
+        <v>3.274</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>47300</v>
       </c>
-      <c r="B44" s="2">
-        <v>66.117000000000004</v>
-      </c>
-      <c r="C44" s="2">
-        <v>3.484</v>
+      <c r="B44">
+        <v>65.233000000000004</v>
+      </c>
+      <c r="C44">
+        <v>3.4860000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>47331</v>
       </c>
-      <c r="B45" s="2">
-        <v>65.960999999999999</v>
-      </c>
-      <c r="C45" s="2">
-        <v>3.5449999999999999</v>
+      <c r="B45">
+        <v>65.129000000000005</v>
+      </c>
+      <c r="C45">
+        <v>3.5459999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>47362</v>
       </c>
-      <c r="B46" s="2">
-        <v>65.831999999999994</v>
-      </c>
-      <c r="C46" s="2">
-        <v>3.532</v>
+      <c r="B46">
+        <v>65.054000000000002</v>
+      </c>
+      <c r="C46">
+        <v>3.5310000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>47392</v>
       </c>
-      <c r="B47" s="2">
-        <v>65.706999999999994</v>
-      </c>
-      <c r="C47" s="2">
-        <v>3.5979999999999999</v>
+      <c r="B47">
+        <v>65.001999999999995</v>
+      </c>
+      <c r="C47">
+        <v>3.5960000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47423</v>
       </c>
-      <c r="B48" s="2">
-        <v>65.540999999999997</v>
-      </c>
-      <c r="C48" s="2">
-        <v>3.758</v>
+      <c r="B48">
+        <v>64.914000000000001</v>
+      </c>
+      <c r="C48">
+        <v>3.7530000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47453</v>
       </c>
-      <c r="B49" s="2">
-        <v>65.370999999999995</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="B49">
+        <v>64.784000000000006</v>
+      </c>
+      <c r="C49">
         <v>4.3339999999999996</v>
       </c>
     </row>
@@ -970,66 +970,66 @@
       <c r="A50" s="4">
         <v>47484</v>
       </c>
-      <c r="B50" s="2">
-        <v>65.212999999999994</v>
-      </c>
-      <c r="C50" s="2">
-        <v>4.7759999999999998</v>
+      <c r="B50">
+        <v>64.643000000000001</v>
+      </c>
+      <c r="C50">
+        <v>4.7690000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>47515</v>
       </c>
-      <c r="B51" s="2">
-        <v>65.081999999999994</v>
-      </c>
-      <c r="C51" s="2">
-        <v>4.3470000000000004</v>
+      <c r="B51">
+        <v>64.542000000000002</v>
+      </c>
+      <c r="C51">
+        <v>4.3380000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>47543</v>
       </c>
-      <c r="B52" s="2">
-        <v>64.959999999999994</v>
-      </c>
-      <c r="C52" s="2">
-        <v>3.504</v>
+      <c r="B52">
+        <v>64.453000000000003</v>
+      </c>
+      <c r="C52">
+        <v>3.496</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>47574</v>
       </c>
-      <c r="B53" s="2">
-        <v>64.843000000000004</v>
-      </c>
-      <c r="C53" s="2">
-        <v>3.129</v>
+      <c r="B53">
+        <v>64.370999999999995</v>
+      </c>
+      <c r="C53">
+        <v>3.117</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>47604</v>
       </c>
-      <c r="B54" s="2">
-        <v>64.692999999999998</v>
-      </c>
-      <c r="C54" s="2">
-        <v>3.0830000000000002</v>
+      <c r="B54">
+        <v>64.251999999999995</v>
+      </c>
+      <c r="C54">
+        <v>3.069</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>47635</v>
       </c>
-      <c r="B55" s="2">
-        <v>64.531999999999996</v>
-      </c>
-      <c r="C55" s="2">
-        <v>3.1989999999999998</v>
+      <c r="B55">
+        <v>64.122</v>
+      </c>
+      <c r="C55">
+        <v>3.1850000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1365,7 +1365,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:B85" numberStoredAsText="1"/>
+    <ignoredError sqref="A56:B85 A2:A55" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>